--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R6" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R7" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R6" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R7" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R6" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R7" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B6" t="n">
         <v>98632</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R6" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B7" t="n">
         <v>98632</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R7" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R6" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R7" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B6" t="n">
         <v>98636</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R6" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B7" t="n">
         <v>98636</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R7" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R6" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R7" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R6" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B7" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R7" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B6" t="n">
         <v>98651</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R6" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B7" t="n">
         <v>98651</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R7" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128570503</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128569922</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128571704</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128570064</v>
+        <v>128569401</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536944</v>
+        <v>536956</v>
       </c>
       <c r="R6" t="n">
-        <v>6983711</v>
+        <v>6983754</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R7" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>128569696</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128569156</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128570503</v>
+        <v>128569401</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536946</v>
+        <v>536956</v>
       </c>
       <c r="R3" t="n">
-        <v>6983707</v>
+        <v>6983754</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128569922</v>
+        <v>128569696</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536957</v>
+        <v>536946</v>
       </c>
       <c r="R4" t="n">
-        <v>6983733</v>
+        <v>6983742</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128571704</v>
+        <v>128569920</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536890</v>
+        <v>536957</v>
       </c>
       <c r="R5" t="n">
-        <v>6983758</v>
+        <v>6983733</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128569401</v>
+        <v>128570064</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536956</v>
+        <v>536944</v>
       </c>
       <c r="R6" t="n">
-        <v>6983754</v>
+        <v>6983711</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128570064</v>
+        <v>128570502</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536944</v>
+        <v>536946</v>
       </c>
       <c r="R7" t="n">
-        <v>6983711</v>
+        <v>6983707</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128569696</v>
+        <v>128571704</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536946</v>
+        <v>536890</v>
       </c>
       <c r="R8" t="n">
-        <v>6983742</v>
+        <v>6983758</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 9816-2024 artfynd.xlsx
+++ b/artfynd/A 9816-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128569156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128569401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128569696</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128569920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128570064</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128570502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,8 +1456,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128571704</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>